--- a/docs/eu/StructureDefinition-CompositionEu.xlsx
+++ b/docs/eu/StructureDefinition-CompositionEu.xlsx
@@ -500,7 +500,7 @@
     <t>informationRecipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient|0.1.1}
+    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient|1.2.0}
 </t>
   </si>
   <si>
